--- a/artfynd/S 2737-2022 artfynd.xlsx
+++ b/artfynd/S 2737-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/260510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/261028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/261618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480815</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/681684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Ekoxeuppropet 2013</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16880267</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118321</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118322</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119953</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119954</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119955</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2447,6 +2527,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119957</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2557,6 +2642,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119958</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2667,6 +2757,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120073</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2777,6 +2872,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120074</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120075</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120076</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3112,6 +3222,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3222,8 +3337,38 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>